--- a/Construction_Project_Data_Management.xlsx
+++ b/Construction_Project_Data_Management.xlsx
@@ -14,8 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NCR Quality Tracker" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Report" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Validation Log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup Tables" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions &amp; Guide" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Submission Tracker" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meeting Log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup Tables" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power BI Export" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions &amp; Guide" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="DisciplineLeadTable">'Lookup Tables'!$A$6:$B$14</definedName>
@@ -32,6 +35,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Monthly Report'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Data Validation Log'!$A$4:$K$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Data Validation Log'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Submission Tracker'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Meeting Log'!$3:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Power BI Export'!$A$3:$R$53</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Power BI Export'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +55,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -157,12 +164,40 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0014532D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0078350F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="002563EB"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -217,6 +252,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -316,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,7 +391,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -366,7 +406,7 @@
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -450,11 +490,56 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1726,6 +1811,73 @@
 </table>
 </file>
 
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblSubmissionTracker" displayName="tblSubmissionTracker" ref="A3:L11" headerRowCount="1">
+  <autoFilter ref="A3:L11"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Discipline"/>
+    <tableColumn id="2" name="Wk 15_x000a_14-Apr"/>
+    <tableColumn id="3" name="Wk 16_x000a_21-Apr"/>
+    <tableColumn id="4" name="Wk 17_x000a_28-Apr"/>
+    <tableColumn id="5" name="Wk 18_x000a_05-May"/>
+    <tableColumn id="6" name="Wk 19_x000a_12-May"/>
+    <tableColumn id="7" name="Wk 20_x000a_19-May"/>
+    <tableColumn id="8" name="Wk 21_x000a_26-May"/>
+    <tableColumn id="9" name="Wk 22_x000a_02-Jun"/>
+    <tableColumn id="10" name="Wk 23_x000a_09-Jun"/>
+    <tableColumn id="11" name="Wk 24_x000a_16-Jun"/>
+    <tableColumn id="12" name="Submissions_x000a_Complete"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblMeetingLog" displayName="tblMeetingLog" ref="A3:J11" headerRowCount="1">
+  <autoFilter ref="A3:J11"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Mtg #"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="Meeting Type"/>
+    <tableColumn id="4" name="Chairperson"/>
+    <tableColumn id="5" name="Attendees (Disciplines)"/>
+    <tableColumn id="6" name="Agenda Item"/>
+    <tableColumn id="7" name="Discussion Summary"/>
+    <tableColumn id="8" name="Decision / Resolution"/>
+    <tableColumn id="9" name="Action IDs Raised"/>
+    <tableColumn id="10" name="Next Meeting Date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tblPowerBI_Export" displayName="tblPowerBI_Export" ref="A3:R53" headerRowCount="1">
+  <autoFilter ref="A3:R53"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="Source_Sheet"/>
+    <tableColumn id="2" name="Record_ID"/>
+    <tableColumn id="3" name="Discipline"/>
+    <tableColumn id="4" name="Responsible_Lead"/>
+    <tableColumn id="5" name="Activity_Description"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Priority_Level"/>
+    <tableColumn id="8" name="Planned_Pct"/>
+    <tableColumn id="9" name="Actual_Pct"/>
+    <tableColumn id="10" name="Variance_Pct"/>
+    <tableColumn id="11" name="Planned_Start"/>
+    <tableColumn id="12" name="Planned_Finish"/>
+    <tableColumn id="13" name="Due_Date"/>
+    <tableColumn id="14" name="Date_Raised"/>
+    <tableColumn id="15" name="Risk_Score"/>
+    <tableColumn id="16" name="Risk_Level"/>
+    <tableColumn id="17" name="Days_Overdue"/>
+    <tableColumn id="18" name="Month_Period"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3045,6 +3197,4843 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00334155"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOOKUP TABLES — Reference Data for Formula Calculations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Powers VLOOKUP · XLOOKUP · INDEX/MATCH across all sheets. Do not rename or delete this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TABLE 1 · Discipline → Lead Person  (VLOOKUP / XLOOKUP / INDEX-MATCH reference)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>TABLE 2 · Risk Score Reference  (IFS formula band reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Lead Person</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Dept. Code</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Min Score</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Max Score</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>SLA Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>J. Hansen</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>j.hansen@project.com</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>Immediate action</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>K. Lindqvist</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>k.lindqvist@project.com</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Action within 14 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>M. Berg</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>m.berg@project.com</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Monitor monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A. Nilsen</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>MEC</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>a.nilsen@project.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>T. Eriksson</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>t.eriksson@project.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>S. Patel</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>PIP</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>s.patel@project.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>HVA</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>l.andersen@project.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Scaffolding</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>R. Kowalski</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>r.kowalski@project.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>J. Hansen</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>j.hansen@project.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TABLE 3 · Status Definitions &amp; Dropdown Values</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>TABLE 4 · Formula Index — Where Each Advanced Function Is Used</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Applies To</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Final?</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Actions / Risks / NCRs</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Raised, no action started</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="H18" s="15">
+        <f>H-G</f>
+        <v/>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>Auto variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Actions / NCRs</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Work underway</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>IF nested</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>Auto status logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Fully resolved and verified</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Responsible</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>XLOOKUP</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>From Lookup Tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Overdue</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>Past due date — escalate</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>Risk Score</t>
+        </is>
+      </c>
+      <c r="H21" s="20">
+        <f>E×F</f>
+        <v/>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>Auto P×I</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Elevated to senior management</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Risk Level</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>IF nested</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>From score</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Mitigated</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Mitigation complete; monitoring</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>Responsible</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>VLOOKUP</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>From Lookup Tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Blocked — awaiting input</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Days Overdue</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>IF/TODAY()</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>Live days past due</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>NCR Tracker</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>IF/TODAY()</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>Live days since raised</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>NCR Tracker</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Discipline Lead</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>INDEX/MATCH</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>From Lookup Tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>Monthly Report</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>Schedule Var %</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>IFERROR/()</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>Auto SV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Monthly Report</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Cost Var %</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>IFERROR/()</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>Auto CV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>Monthly Report</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>Discipline Lead</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>INDEX/MATCH</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>From Lookup Tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>All KPIs</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>COUNTIF</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>Live from data sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>Discipline table</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>AVERAGEIF</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>Live pull per discipline</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Monthly summary</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>SUMIFS</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>Multi-criteria totals</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="A16:D16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002563EB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>POWER BI EXPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Flat denormalised dataset — import into Power BI via  Get Data → Excel Workbook → tblPowerBI_Export</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Source_Sheet</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Record_ID</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Responsible_Lead</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Activity_Description</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Priority_Level</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Planned_Pct</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Actual_Pct</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Variance_Pct</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>Planned_Start</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>Planned_Finish</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>Due_Date</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Date_Raised</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>Risk_Score</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>Risk_Level</t>
+        </is>
+      </c>
+      <c r="Q3" s="11" t="inlineStr">
+        <is>
+          <t>Days_Overdue</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="inlineStr">
+        <is>
+          <t>Month_Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="inlineStr">
+        <is>
+          <t>WP-01</t>
+        </is>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>Earthworks &amp; Site Levelling</t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G4" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L4" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O4" s="57" t="n"/>
+      <c r="P4" s="52" t="n"/>
+      <c r="Q4" s="57" t="n"/>
+      <c r="R4" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>WP-02</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>Foundation Piling</t>
+        </is>
+      </c>
+      <c r="F5" s="54" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G5" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="58" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I5" s="58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J5" s="58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K5" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L5" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M5" s="55" t="n"/>
+      <c r="N5" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O5" s="59" t="n"/>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="59" t="n"/>
+      <c r="R5" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>WP-03</t>
+        </is>
+      </c>
+      <c r="C6" s="52" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>Drainage &amp; Culverts</t>
+        </is>
+      </c>
+      <c r="F6" s="52" t="inlineStr">
+        <is>
+          <t>Behind</t>
+        </is>
+      </c>
+      <c r="G6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J6" s="56" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K6" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L6" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M6" s="53" t="n"/>
+      <c r="N6" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O6" s="57" t="n"/>
+      <c r="P6" s="52" t="n"/>
+      <c r="Q6" s="57" t="n"/>
+      <c r="R6" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>WP-04</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>Steel Frame Erection</t>
+        </is>
+      </c>
+      <c r="F7" s="54" t="inlineStr">
+        <is>
+          <t>Ahead</t>
+        </is>
+      </c>
+      <c r="G7" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="58" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J7" s="58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K7" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L7" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M7" s="55" t="n"/>
+      <c r="N7" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O7" s="59" t="n"/>
+      <c r="P7" s="54" t="n"/>
+      <c r="Q7" s="59" t="n"/>
+      <c r="R7" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>WP-05</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>Secondary Steelwork</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I8" s="56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" s="56" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K8" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L8" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M8" s="53" t="n"/>
+      <c r="N8" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O8" s="57" t="n"/>
+      <c r="P8" s="52" t="n"/>
+      <c r="Q8" s="57" t="n"/>
+      <c r="R8" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>WP-06</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>Bolting &amp; Torquing</t>
+        </is>
+      </c>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" s="58" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J9" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K9" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L9" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M9" s="55" t="n"/>
+      <c r="N9" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O9" s="59" t="n"/>
+      <c r="P9" s="54" t="n"/>
+      <c r="Q9" s="59" t="n"/>
+      <c r="R9" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="inlineStr">
+        <is>
+          <t>WP-07</t>
+        </is>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>Main HV Cabling</t>
+        </is>
+      </c>
+      <c r="F10" s="52" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I10" s="56" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J10" s="56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K10" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L10" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M10" s="53" t="n"/>
+      <c r="N10" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O10" s="57" t="n"/>
+      <c r="P10" s="52" t="n"/>
+      <c r="Q10" s="57" t="n"/>
+      <c r="R10" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>WP-08</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>LV Distribution Boards</t>
+        </is>
+      </c>
+      <c r="F11" s="54" t="inlineStr">
+        <is>
+          <t>Behind</t>
+        </is>
+      </c>
+      <c r="G11" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="58" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J11" s="58" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K11" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L11" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M11" s="55" t="n"/>
+      <c r="N11" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O11" s="59" t="n"/>
+      <c r="P11" s="54" t="n"/>
+      <c r="Q11" s="59" t="n"/>
+      <c r="R11" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>WP-09</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>Earthing &amp; Lightning Protection</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="56" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I12" s="56" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J12" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L12" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M12" s="53" t="n"/>
+      <c r="N12" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O12" s="57" t="n"/>
+      <c r="P12" s="52" t="n"/>
+      <c r="Q12" s="57" t="n"/>
+      <c r="R12" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>WP-10</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>R. Johansen</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>Equipment Setting &amp; Alignment</t>
+        </is>
+      </c>
+      <c r="F13" s="54" t="inlineStr">
+        <is>
+          <t>Ahead</t>
+        </is>
+      </c>
+      <c r="G13" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I13" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K13" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L13" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M13" s="55" t="n"/>
+      <c r="N13" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O13" s="59" t="n"/>
+      <c r="P13" s="54" t="n"/>
+      <c r="Q13" s="59" t="n"/>
+      <c r="R13" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="inlineStr">
+        <is>
+          <t>WP-11</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>R. Johansen</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>Piping Spools Fit-Up</t>
+        </is>
+      </c>
+      <c r="F14" s="52" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="56" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J14" s="56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K14" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L14" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M14" s="53" t="n"/>
+      <c r="N14" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O14" s="57" t="n"/>
+      <c r="P14" s="52" t="n"/>
+      <c r="Q14" s="57" t="n"/>
+      <c r="R14" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>WP-12</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
+        <is>
+          <t>T. Eriksen</t>
+        </is>
+      </c>
+      <c r="E15" s="54" t="inlineStr">
+        <is>
+          <t>Main Process Lines</t>
+        </is>
+      </c>
+      <c r="F15" s="54" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G15" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I15" s="58" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J15" s="58" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="K15" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L15" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M15" s="55" t="n"/>
+      <c r="N15" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O15" s="59" t="n"/>
+      <c r="P15" s="54" t="n"/>
+      <c r="Q15" s="59" t="n"/>
+      <c r="R15" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>WP-13</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>T. Eriksen</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="inlineStr">
+        <is>
+          <t>Utility Lines</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>Behind</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I16" s="56" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J16" s="56" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K16" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L16" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M16" s="53" t="n"/>
+      <c r="N16" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O16" s="57" t="n"/>
+      <c r="P16" s="52" t="n"/>
+      <c r="Q16" s="57" t="n"/>
+      <c r="R16" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>WP-14</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr">
+        <is>
+          <t>S. Larsen</t>
+        </is>
+      </c>
+      <c r="E17" s="54" t="inlineStr">
+        <is>
+          <t>Field Instruments Install</t>
+        </is>
+      </c>
+      <c r="F17" s="54" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G17" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I17" s="58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L17" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M17" s="55" t="n"/>
+      <c r="N17" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O17" s="59" t="n"/>
+      <c r="P17" s="54" t="n"/>
+      <c r="Q17" s="59" t="n"/>
+      <c r="R17" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>WP-15</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>S. Larsen</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>Control Cable Pulling</t>
+        </is>
+      </c>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G18" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L18" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M18" s="53" t="n"/>
+      <c r="N18" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O18" s="57" t="n"/>
+      <c r="P18" s="52" t="n"/>
+      <c r="Q18" s="57" t="n"/>
+      <c r="R18" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B19" s="54" t="inlineStr">
+        <is>
+          <t>WP-16</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>M. Olsen</t>
+        </is>
+      </c>
+      <c r="E19" s="54" t="inlineStr">
+        <is>
+          <t>Ductwork Fabrication</t>
+        </is>
+      </c>
+      <c r="F19" s="54" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="G19" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I19" s="58" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J19" s="58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K19" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L19" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M19" s="55" t="n"/>
+      <c r="N19" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O19" s="59" t="n"/>
+      <c r="P19" s="54" t="n"/>
+      <c r="Q19" s="59" t="n"/>
+      <c r="R19" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>WP-17</t>
+        </is>
+      </c>
+      <c r="C20" s="52" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D20" s="52" t="inlineStr">
+        <is>
+          <t>M. Olsen</t>
+        </is>
+      </c>
+      <c r="E20" s="52" t="inlineStr">
+        <is>
+          <t>AHU Installation</t>
+        </is>
+      </c>
+      <c r="F20" s="52" t="inlineStr">
+        <is>
+          <t>Ahead</t>
+        </is>
+      </c>
+      <c r="G20" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="56" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I20" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="56" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K20" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L20" s="53" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M20" s="53" t="n"/>
+      <c r="N20" s="53" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O20" s="57" t="n"/>
+      <c r="P20" s="52" t="n"/>
+      <c r="Q20" s="57" t="n"/>
+      <c r="R20" s="52" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>WP-18</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>Scaffolding</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>B. Dahl</t>
+        </is>
+      </c>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>Access Scaffold — Zone A</t>
+        </is>
+      </c>
+      <c r="F21" s="54" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G21" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L21" s="55" t="n">
+        <v>46173</v>
+      </c>
+      <c r="M21" s="55" t="n"/>
+      <c r="N21" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O21" s="59" t="n"/>
+      <c r="P21" s="54" t="n"/>
+      <c r="Q21" s="59" t="n"/>
+      <c r="R21" s="54" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>RR-01</t>
+        </is>
+      </c>
+      <c r="C22" s="52" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D22" s="52" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E22" s="52" t="inlineStr">
+        <is>
+          <t>Ground Settlement — Soft Strata</t>
+        </is>
+      </c>
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G22" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H22" s="56" t="n"/>
+      <c r="I22" s="56" t="n"/>
+      <c r="J22" s="56" t="n"/>
+      <c r="K22" s="53" t="n"/>
+      <c r="L22" s="53" t="n"/>
+      <c r="M22" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N22" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O22" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="P22" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q22" s="57" t="n"/>
+      <c r="R22" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>RR-02</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
+          <t>Excavation Collapse — Adjacent Services</t>
+        </is>
+      </c>
+      <c r="F23" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G23" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H23" s="58" t="n"/>
+      <c r="I23" s="58" t="n"/>
+      <c r="J23" s="58" t="n"/>
+      <c r="K23" s="55" t="n"/>
+      <c r="L23" s="55" t="n"/>
+      <c r="M23" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N23" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O23" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="P23" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q23" s="59" t="n"/>
+      <c r="R23" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>RR-03</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E24" s="52" t="inlineStr">
+        <is>
+          <t>Material Delivery Delay — Structural Steel</t>
+        </is>
+      </c>
+      <c r="F24" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G24" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H24" s="56" t="n"/>
+      <c r="I24" s="56" t="n"/>
+      <c r="J24" s="56" t="n"/>
+      <c r="K24" s="53" t="n"/>
+      <c r="L24" s="53" t="n"/>
+      <c r="M24" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N24" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O24" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q24" s="57" t="n"/>
+      <c r="R24" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>RR-04</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E25" s="54" t="inlineStr">
+        <is>
+          <t>Crane Overload During Lift</t>
+        </is>
+      </c>
+      <c r="F25" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G25" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H25" s="58" t="n"/>
+      <c r="I25" s="58" t="n"/>
+      <c r="J25" s="58" t="n"/>
+      <c r="K25" s="55" t="n"/>
+      <c r="L25" s="55" t="n"/>
+      <c r="M25" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N25" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O25" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q25" s="59" t="n"/>
+      <c r="R25" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B26" s="52" t="inlineStr">
+        <is>
+          <t>RR-05</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E26" s="52" t="inlineStr">
+        <is>
+          <t>HV Cable Damage During Excavation</t>
+        </is>
+      </c>
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G26" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H26" s="56" t="n"/>
+      <c r="I26" s="56" t="n"/>
+      <c r="J26" s="56" t="n"/>
+      <c r="K26" s="53" t="n"/>
+      <c r="L26" s="53" t="n"/>
+      <c r="M26" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N26" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O26" s="57" t="n">
+        <v>16</v>
+      </c>
+      <c r="P26" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q26" s="57" t="n"/>
+      <c r="R26" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>RR-06</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>Switchgear Procurement Lead Time</t>
+        </is>
+      </c>
+      <c r="F27" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G27" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H27" s="58" t="n"/>
+      <c r="I27" s="58" t="n"/>
+      <c r="J27" s="58" t="n"/>
+      <c r="K27" s="55" t="n"/>
+      <c r="L27" s="55" t="n"/>
+      <c r="M27" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N27" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O27" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="P27" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q27" s="59" t="n"/>
+      <c r="R27" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>RR-07</t>
+        </is>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>R. Johansen</t>
+        </is>
+      </c>
+      <c r="E28" s="52" t="inlineStr">
+        <is>
+          <t>Equipment Alignment Tolerance Exceeded</t>
+        </is>
+      </c>
+      <c r="F28" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G28" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H28" s="56" t="n"/>
+      <c r="I28" s="56" t="n"/>
+      <c r="J28" s="56" t="n"/>
+      <c r="K28" s="53" t="n"/>
+      <c r="L28" s="53" t="n"/>
+      <c r="M28" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N28" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O28" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q28" s="57" t="n"/>
+      <c r="R28" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>RR-08</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>T. Eriksen</t>
+        </is>
+      </c>
+      <c r="E29" s="54" t="inlineStr">
+        <is>
+          <t>Pressure Test Failure — Flange Leak</t>
+        </is>
+      </c>
+      <c r="F29" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G29" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H29" s="58" t="n"/>
+      <c r="I29" s="58" t="n"/>
+      <c r="J29" s="58" t="n"/>
+      <c r="K29" s="55" t="n"/>
+      <c r="L29" s="55" t="n"/>
+      <c r="M29" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N29" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O29" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="P29" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q29" s="59" t="n"/>
+      <c r="R29" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>RR-09</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>T. Eriksen</t>
+        </is>
+      </c>
+      <c r="E30" s="52" t="inlineStr">
+        <is>
+          <t>Wrong Material Delivered — Grade Mismatch</t>
+        </is>
+      </c>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G30" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H30" s="56" t="n"/>
+      <c r="I30" s="56" t="n"/>
+      <c r="J30" s="56" t="n"/>
+      <c r="K30" s="53" t="n"/>
+      <c r="L30" s="53" t="n"/>
+      <c r="M30" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N30" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O30" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" s="52" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q30" s="57" t="n"/>
+      <c r="R30" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B31" s="54" t="inlineStr">
+        <is>
+          <t>RR-10</t>
+        </is>
+      </c>
+      <c r="C31" s="54" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>S. Larsen</t>
+        </is>
+      </c>
+      <c r="E31" s="54" t="inlineStr">
+        <is>
+          <t>Calibration Drift — Pressure Transmitters</t>
+        </is>
+      </c>
+      <c r="F31" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G31" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H31" s="58" t="n"/>
+      <c r="I31" s="58" t="n"/>
+      <c r="J31" s="58" t="n"/>
+      <c r="K31" s="55" t="n"/>
+      <c r="L31" s="55" t="n"/>
+      <c r="M31" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N31" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O31" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="P31" s="54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q31" s="59" t="n"/>
+      <c r="R31" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="inlineStr">
+        <is>
+          <t>RR-11</t>
+        </is>
+      </c>
+      <c r="C32" s="52" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D32" s="52" t="inlineStr">
+        <is>
+          <t>M. Olsen</t>
+        </is>
+      </c>
+      <c r="E32" s="52" t="inlineStr">
+        <is>
+          <t>Ductwork Fabrication Error</t>
+        </is>
+      </c>
+      <c r="F32" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G32" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="56" t="n"/>
+      <c r="I32" s="56" t="n"/>
+      <c r="J32" s="56" t="n"/>
+      <c r="K32" s="53" t="n"/>
+      <c r="L32" s="53" t="n"/>
+      <c r="M32" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N32" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O32" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" s="52" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q32" s="57" t="n"/>
+      <c r="R32" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B33" s="54" t="inlineStr">
+        <is>
+          <t>RR-12</t>
+        </is>
+      </c>
+      <c r="C33" s="54" t="inlineStr">
+        <is>
+          <t>Scaffolding</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>B. Dahl</t>
+        </is>
+      </c>
+      <c r="E33" s="54" t="inlineStr">
+        <is>
+          <t>Scaffold Overloading</t>
+        </is>
+      </c>
+      <c r="F33" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G33" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H33" s="58" t="n"/>
+      <c r="I33" s="58" t="n"/>
+      <c r="J33" s="58" t="n"/>
+      <c r="K33" s="55" t="n"/>
+      <c r="L33" s="55" t="n"/>
+      <c r="M33" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N33" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O33" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="P33" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q33" s="59" t="n"/>
+      <c r="R33" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="inlineStr">
+        <is>
+          <t>RR-13</t>
+        </is>
+      </c>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D34" s="52" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E34" s="52" t="inlineStr">
+        <is>
+          <t>Environmental Runoff — Site Drainage</t>
+        </is>
+      </c>
+      <c r="F34" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G34" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H34" s="56" t="n"/>
+      <c r="I34" s="56" t="n"/>
+      <c r="J34" s="56" t="n"/>
+      <c r="K34" s="53" t="n"/>
+      <c r="L34" s="53" t="n"/>
+      <c r="M34" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N34" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O34" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="P34" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q34" s="57" t="n"/>
+      <c r="R34" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="54" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B35" s="54" t="inlineStr">
+        <is>
+          <t>RR-14</t>
+        </is>
+      </c>
+      <c r="C35" s="54" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E35" s="54" t="inlineStr">
+        <is>
+          <t>Electrical Isolation Procedure Breach</t>
+        </is>
+      </c>
+      <c r="F35" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G35" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H35" s="58" t="n"/>
+      <c r="I35" s="58" t="n"/>
+      <c r="J35" s="58" t="n"/>
+      <c r="K35" s="55" t="n"/>
+      <c r="L35" s="55" t="n"/>
+      <c r="M35" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N35" s="55" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O35" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="P35" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q35" s="59" t="n"/>
+      <c r="R35" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="52" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="inlineStr">
+        <is>
+          <t>RR-15</t>
+        </is>
+      </c>
+      <c r="C36" s="52" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D36" s="52" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E36" s="52" t="inlineStr">
+        <is>
+          <t>Weld Inspection Failure — NDT</t>
+        </is>
+      </c>
+      <c r="F36" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G36" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H36" s="56" t="n"/>
+      <c r="I36" s="56" t="n"/>
+      <c r="J36" s="56" t="n"/>
+      <c r="K36" s="53" t="n"/>
+      <c r="L36" s="53" t="n"/>
+      <c r="M36" s="53" t="n">
+        <v>46157</v>
+      </c>
+      <c r="N36" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O36" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="P36" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q36" s="57" t="n"/>
+      <c r="R36" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B37" s="54" t="inlineStr">
+        <is>
+          <t>AI-01</t>
+        </is>
+      </c>
+      <c r="C37" s="54" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E37" s="54" t="inlineStr">
+        <is>
+          <t>Submit updated ITP to QA Manager</t>
+        </is>
+      </c>
+      <c r="F37" s="54" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G37" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H37" s="58" t="n"/>
+      <c r="I37" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="58" t="n"/>
+      <c r="K37" s="55" t="n"/>
+      <c r="L37" s="55" t="n"/>
+      <c r="M37" s="55" t="n">
+        <v>46044</v>
+      </c>
+      <c r="N37" s="55" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O37" s="59" t="n"/>
+      <c r="P37" s="54" t="n"/>
+      <c r="Q37" s="59" t="n"/>
+      <c r="R37" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="inlineStr">
+        <is>
+          <t>AI-02</t>
+        </is>
+      </c>
+      <c r="C38" s="52" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D38" s="52" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E38" s="52" t="inlineStr">
+        <is>
+          <t>Complete pre-pour checklist — Footing A</t>
+        </is>
+      </c>
+      <c r="F38" s="52" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G38" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H38" s="56" t="n"/>
+      <c r="I38" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="56" t="n"/>
+      <c r="K38" s="53" t="n"/>
+      <c r="L38" s="53" t="n"/>
+      <c r="M38" s="53" t="n">
+        <v>46050</v>
+      </c>
+      <c r="N38" s="53" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O38" s="57" t="n"/>
+      <c r="P38" s="52" t="n"/>
+      <c r="Q38" s="57" t="n"/>
+      <c r="R38" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t>AI-03</t>
+        </is>
+      </c>
+      <c r="C39" s="54" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D39" s="54" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E39" s="54" t="inlineStr">
+        <is>
+          <t>Resolve NCR-003 bolt torque issue</t>
+        </is>
+      </c>
+      <c r="F39" s="54" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G39" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H39" s="58" t="n"/>
+      <c r="I39" s="58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J39" s="58" t="n"/>
+      <c r="K39" s="55" t="n"/>
+      <c r="L39" s="55" t="n"/>
+      <c r="M39" s="55" t="n">
+        <v>46073</v>
+      </c>
+      <c r="N39" s="55" t="n">
+        <v>46054</v>
+      </c>
+      <c r="O39" s="59" t="n"/>
+      <c r="P39" s="54" t="n"/>
+      <c r="Q39" s="59" t="n">
+        <v>73</v>
+      </c>
+      <c r="R39" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="inlineStr">
+        <is>
+          <t>AI-04</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D40" s="52" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E40" s="52" t="inlineStr">
+        <is>
+          <t>Update as-built drawings — Grid C</t>
+        </is>
+      </c>
+      <c r="F40" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G40" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H40" s="56" t="n"/>
+      <c r="I40" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="56" t="n"/>
+      <c r="K40" s="53" t="n"/>
+      <c r="L40" s="53" t="n"/>
+      <c r="M40" s="53" t="n">
+        <v>46086</v>
+      </c>
+      <c r="N40" s="53" t="n">
+        <v>46063</v>
+      </c>
+      <c r="O40" s="57" t="n"/>
+      <c r="P40" s="52" t="n"/>
+      <c r="Q40" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="R40" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>AI-05</t>
+        </is>
+      </c>
+      <c r="C41" s="54" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E41" s="54" t="inlineStr">
+        <is>
+          <t>Submit HV cable routing revision</t>
+        </is>
+      </c>
+      <c r="F41" s="54" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G41" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H41" s="58" t="n"/>
+      <c r="I41" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J41" s="58" t="n"/>
+      <c r="K41" s="55" t="n"/>
+      <c r="L41" s="55" t="n"/>
+      <c r="M41" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="N41" s="55" t="n">
+        <v>46067</v>
+      </c>
+      <c r="O41" s="59" t="n"/>
+      <c r="P41" s="54" t="n"/>
+      <c r="Q41" s="59" t="n">
+        <v>64</v>
+      </c>
+      <c r="R41" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B42" s="52" t="inlineStr">
+        <is>
+          <t>AI-06</t>
+        </is>
+      </c>
+      <c r="C42" s="52" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D42" s="52" t="inlineStr">
+        <is>
+          <t>L. Andersen</t>
+        </is>
+      </c>
+      <c r="E42" s="52" t="inlineStr">
+        <is>
+          <t>Thermographic survey — DB01 &amp; DB02</t>
+        </is>
+      </c>
+      <c r="F42" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G42" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H42" s="56" t="n"/>
+      <c r="I42" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="56" t="n"/>
+      <c r="K42" s="53" t="n"/>
+      <c r="L42" s="53" t="n"/>
+      <c r="M42" s="53" t="n">
+        <v>46096</v>
+      </c>
+      <c r="N42" s="53" t="n">
+        <v>46073</v>
+      </c>
+      <c r="O42" s="57" t="n"/>
+      <c r="P42" s="52" t="n"/>
+      <c r="Q42" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="R42" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B43" s="54" t="inlineStr">
+        <is>
+          <t>AI-07</t>
+        </is>
+      </c>
+      <c r="C43" s="54" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="D43" s="54" t="inlineStr">
+        <is>
+          <t>R. Johansen</t>
+        </is>
+      </c>
+      <c r="E43" s="54" t="inlineStr">
+        <is>
+          <t>Pump alignment report — sign off</t>
+        </is>
+      </c>
+      <c r="F43" s="54" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G43" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H43" s="58" t="n"/>
+      <c r="I43" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="58" t="n"/>
+      <c r="K43" s="55" t="n"/>
+      <c r="L43" s="55" t="n"/>
+      <c r="M43" s="55" t="n">
+        <v>46058</v>
+      </c>
+      <c r="N43" s="55" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O43" s="59" t="n"/>
+      <c r="P43" s="54" t="n"/>
+      <c r="Q43" s="59" t="n"/>
+      <c r="R43" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B44" s="52" t="inlineStr">
+        <is>
+          <t>AI-08</t>
+        </is>
+      </c>
+      <c r="C44" s="52" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="D44" s="52" t="inlineStr">
+        <is>
+          <t>R. Johansen</t>
+        </is>
+      </c>
+      <c r="E44" s="52" t="inlineStr">
+        <is>
+          <t>Torque log update — all flanges</t>
+        </is>
+      </c>
+      <c r="F44" s="52" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G44" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H44" s="56" t="n"/>
+      <c r="I44" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J44" s="56" t="n"/>
+      <c r="K44" s="53" t="n"/>
+      <c r="L44" s="53" t="n"/>
+      <c r="M44" s="53" t="n">
+        <v>46091</v>
+      </c>
+      <c r="N44" s="53" t="n">
+        <v>46058</v>
+      </c>
+      <c r="O44" s="57" t="n"/>
+      <c r="P44" s="52" t="n"/>
+      <c r="Q44" s="57" t="n">
+        <v>55</v>
+      </c>
+      <c r="R44" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B45" s="54" t="inlineStr">
+        <is>
+          <t>AI-09</t>
+        </is>
+      </c>
+      <c r="C45" s="54" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="D45" s="54" t="inlineStr">
+        <is>
+          <t>T. Eriksen</t>
+        </is>
+      </c>
+      <c r="E45" s="54" t="inlineStr">
+        <is>
+          <t>Pressure test schedule — submit to client</t>
+        </is>
+      </c>
+      <c r="F45" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G45" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H45" s="58" t="n"/>
+      <c r="I45" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="58" t="n"/>
+      <c r="K45" s="55" t="n"/>
+      <c r="L45" s="55" t="n"/>
+      <c r="M45" s="55" t="n">
+        <v>46101</v>
+      </c>
+      <c r="N45" s="55" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O45" s="59" t="n"/>
+      <c r="P45" s="54" t="n"/>
+      <c r="Q45" s="59" t="n">
+        <v>45</v>
+      </c>
+      <c r="R45" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B46" s="52" t="inlineStr">
+        <is>
+          <t>AI-10</t>
+        </is>
+      </c>
+      <c r="C46" s="52" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="D46" s="52" t="inlineStr">
+        <is>
+          <t>T. Eriksen</t>
+        </is>
+      </c>
+      <c r="E46" s="52" t="inlineStr">
+        <is>
+          <t>Reinstate insulation — Line 12B</t>
+        </is>
+      </c>
+      <c r="F46" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G46" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H46" s="56" t="n"/>
+      <c r="I46" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="56" t="n"/>
+      <c r="K46" s="53" t="n"/>
+      <c r="L46" s="53" t="n"/>
+      <c r="M46" s="53" t="n">
+        <v>46106</v>
+      </c>
+      <c r="N46" s="53" t="n">
+        <v>46075</v>
+      </c>
+      <c r="O46" s="57" t="n"/>
+      <c r="P46" s="52" t="n"/>
+      <c r="Q46" s="57" t="n">
+        <v>40</v>
+      </c>
+      <c r="R46" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B47" s="54" t="inlineStr">
+        <is>
+          <t>AI-11</t>
+        </is>
+      </c>
+      <c r="C47" s="54" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+      <c r="D47" s="54" t="inlineStr">
+        <is>
+          <t>S. Larsen</t>
+        </is>
+      </c>
+      <c r="E47" s="54" t="inlineStr">
+        <is>
+          <t>Calibration certs — transmitters T01–T08</t>
+        </is>
+      </c>
+      <c r="F47" s="54" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G47" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H47" s="58" t="n"/>
+      <c r="I47" s="58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J47" s="58" t="n"/>
+      <c r="K47" s="55" t="n"/>
+      <c r="L47" s="55" t="n"/>
+      <c r="M47" s="55" t="n">
+        <v>46081</v>
+      </c>
+      <c r="N47" s="55" t="n">
+        <v>46047</v>
+      </c>
+      <c r="O47" s="59" t="n"/>
+      <c r="P47" s="54" t="n"/>
+      <c r="Q47" s="59" t="n">
+        <v>65</v>
+      </c>
+      <c r="R47" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B48" s="52" t="inlineStr">
+        <is>
+          <t>AI-12</t>
+        </is>
+      </c>
+      <c r="C48" s="52" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+      <c r="D48" s="52" t="inlineStr">
+        <is>
+          <t>S. Larsen</t>
+        </is>
+      </c>
+      <c r="E48" s="52" t="inlineStr">
+        <is>
+          <t>Loop test documentation — Zone 2</t>
+        </is>
+      </c>
+      <c r="F48" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G48" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H48" s="56" t="n"/>
+      <c r="I48" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="56" t="n"/>
+      <c r="K48" s="53" t="n"/>
+      <c r="L48" s="53" t="n"/>
+      <c r="M48" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="N48" s="53" t="n">
+        <v>46081</v>
+      </c>
+      <c r="O48" s="57" t="n"/>
+      <c r="P48" s="52" t="n"/>
+      <c r="Q48" s="57" t="n">
+        <v>33</v>
+      </c>
+      <c r="R48" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B49" s="54" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="C49" s="54" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D49" s="54" t="inlineStr">
+        <is>
+          <t>M. Olsen</t>
+        </is>
+      </c>
+      <c r="E49" s="54" t="inlineStr">
+        <is>
+          <t>Damper actuator commissioning test</t>
+        </is>
+      </c>
+      <c r="F49" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G49" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H49" s="58" t="n"/>
+      <c r="I49" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="58" t="n"/>
+      <c r="K49" s="55" t="n"/>
+      <c r="L49" s="55" t="n"/>
+      <c r="M49" s="55" t="n">
+        <v>46122</v>
+      </c>
+      <c r="N49" s="55" t="n">
+        <v>46082</v>
+      </c>
+      <c r="O49" s="59" t="n"/>
+      <c r="P49" s="54" t="n"/>
+      <c r="Q49" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="R49" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B50" s="52" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="C50" s="52" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D50" s="52" t="inlineStr">
+        <is>
+          <t>M. Olsen</t>
+        </is>
+      </c>
+      <c r="E50" s="52" t="inlineStr">
+        <is>
+          <t>Duct leak test — AHU-01 zone</t>
+        </is>
+      </c>
+      <c r="F50" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G50" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H50" s="56" t="n"/>
+      <c r="I50" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="56" t="n"/>
+      <c r="K50" s="53" t="n"/>
+      <c r="L50" s="53" t="n"/>
+      <c r="M50" s="53" t="n">
+        <v>46127</v>
+      </c>
+      <c r="N50" s="53" t="n">
+        <v>46086</v>
+      </c>
+      <c r="O50" s="57" t="n"/>
+      <c r="P50" s="52" t="n"/>
+      <c r="Q50" s="57" t="n">
+        <v>19</v>
+      </c>
+      <c r="R50" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>AI-15</t>
+        </is>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>Scaffolding</t>
+        </is>
+      </c>
+      <c r="D51" s="54" t="inlineStr">
+        <is>
+          <t>B. Dahl</t>
+        </is>
+      </c>
+      <c r="E51" s="54" t="inlineStr">
+        <is>
+          <t>Weekly scaffold inspection log</t>
+        </is>
+      </c>
+      <c r="F51" s="54" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G51" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H51" s="58" t="n"/>
+      <c r="I51" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J51" s="58" t="n"/>
+      <c r="K51" s="55" t="n"/>
+      <c r="L51" s="55" t="n"/>
+      <c r="M51" s="55" t="n">
+        <v>46143</v>
+      </c>
+      <c r="N51" s="55" t="n">
+        <v>46061</v>
+      </c>
+      <c r="O51" s="59" t="n"/>
+      <c r="P51" s="54" t="n"/>
+      <c r="Q51" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="R51" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="52" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B52" s="52" t="inlineStr">
+        <is>
+          <t>AI-16</t>
+        </is>
+      </c>
+      <c r="C52" s="52" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="D52" s="52" t="inlineStr">
+        <is>
+          <t>P. Hansen</t>
+        </is>
+      </c>
+      <c r="E52" s="52" t="inlineStr">
+        <is>
+          <t>Weekly site diary update — all disciplines</t>
+        </is>
+      </c>
+      <c r="F52" s="52" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G52" s="52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H52" s="56" t="n"/>
+      <c r="I52" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J52" s="56" t="n"/>
+      <c r="K52" s="53" t="n"/>
+      <c r="L52" s="53" t="n"/>
+      <c r="M52" s="53" t="n">
+        <v>46150</v>
+      </c>
+      <c r="N52" s="53" t="n">
+        <v>46068</v>
+      </c>
+      <c r="O52" s="57" t="n"/>
+      <c r="P52" s="52" t="n"/>
+      <c r="Q52" s="57" t="n"/>
+      <c r="R52" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="54" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B53" s="54" t="inlineStr">
+        <is>
+          <t>AI-17</t>
+        </is>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="D53" s="54" t="inlineStr">
+        <is>
+          <t>K. Berg</t>
+        </is>
+      </c>
+      <c r="E53" s="54" t="inlineStr">
+        <is>
+          <t>Close out punch list — Zone B steelwork</t>
+        </is>
+      </c>
+      <c r="F53" s="54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G53" s="54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H53" s="58" t="n"/>
+      <c r="I53" s="58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J53" s="58" t="n"/>
+      <c r="K53" s="55" t="n"/>
+      <c r="L53" s="55" t="n"/>
+      <c r="M53" s="55" t="n">
+        <v>46142</v>
+      </c>
+      <c r="N53" s="55" t="n">
+        <v>46091</v>
+      </c>
+      <c r="O53" s="59" t="n"/>
+      <c r="P53" s="54" t="n"/>
+      <c r="Q53" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="60" t="inlineStr">
+        <is>
+          <t>HOW TO IMPORT INTO POWER BI:  Home → Get Data → Excel Workbook → select this file → check  tblPowerBI_Export  → Load   |   Then build visuals using Source_Sheet as slicer, Discipline as axis, Status/Risk_Level as legend.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R53"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A55:R55"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00334155"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WORKBOOK GUIDE — Construction Project Data Management System</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sheet directory, formula reference, color legend, ID conventions, and usage workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SHEET DIRECTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Entry Columns</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Key Formulas</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Lookup Tables</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Reference tables — powers all lookup formulas</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Update when personnel changes</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>When team changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Live project health — KPIs, progress, risk, actions, EV</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Read-only (formula-driven)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>COUNTIF/S, AVERAGEIF, SUMIFS</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Auto on file open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Weekly Progress</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Planned vs. actual % per activity per week</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>G (Planned%) and H (Actual%)</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>IF, XLOOKUP</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Weekly — by Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Risk log with P×I matrix and auto level</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>All except G, H</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>E×F, nested IF</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Weekly minimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Action Item Log</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>All meeting action items with status tracking</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All except F, N</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>VLOOKUP, IF/TODAY()</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>After each meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NCR Quality Tracker</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Non-conformance full lifecycle</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>All except M, N</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>TODAY()−date, INDEX/MATCH</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>As NCRs arise</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Monthly Report</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Budget vs. actual + Earned Value analysis</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>A–H, K–M</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>SV/CV formulas, INDEX/MATCH, SUMIFS</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>2nd working day</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Data Validation Log</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Data quality issues audit trail</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>All columns</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Manual log</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>During validation sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>FORMULA REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Sheet — Column</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>COUNTIF</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Dashboard — KPI tiles</t>
+        </is>
+      </c>
+      <c r="C18" s="15">
+        <f>COUNTIF($I:$I,"Open")</f>
+        <v/>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Count matching single criterion</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>COUNTIFS</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Dashboard — discipline table</t>
+        </is>
+      </c>
+      <c r="C19" s="20">
+        <f>COUNTIFS($E:$E,"Civil",$I:$I,"Open")</f>
+        <v/>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Count matching multiple criteria</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>2007+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>AVERAGEIF</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Dashboard — discipline %</t>
+        </is>
+      </c>
+      <c r="C20" s="15">
+        <f>AVERAGEIF($B:$B,"Civil",$H:$H)</f>
+        <v/>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Average matching one criterion</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>2007+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>SUMIFS</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Dashboard — monthly summary</t>
+        </is>
+      </c>
+      <c r="C21" s="20">
+        <f>SUMIFS($C:$C,$A:$A,"Apr-26")</f>
+        <v/>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>Sum matching multiple criteria</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>2007+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>VLOOKUP</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Action Log — Responsible col</t>
+        </is>
+      </c>
+      <c r="C22" s="15">
+        <f>IFERROR(VLOOKUP(E3,$A$6:$B$14,2,0),"-")</f>
+        <v/>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Lookup value in first column of table</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>XLOOKUP</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Weekly Progress — Responsible</t>
+        </is>
+      </c>
+      <c r="C23" s="20">
+        <f>IFERROR(XLOOKUP(B3,$A$6:$A$14,$B$6:$B$14),"?")</f>
+        <v/>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Flexible; searches any direction</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Excel 365</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>INDEX/MATCH</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>NCR &amp; Monthly — Disc. Lead</t>
+        </is>
+      </c>
+      <c r="C24" s="15">
+        <f>INDEX($B$6:$B$14,MATCH(B3,$A$6:$A$14,0))</f>
+        <v/>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Flexible alternative to VLOOKUP</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>IF nested</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Weekly Progress — Status col</t>
+        </is>
+      </c>
+      <c r="C25" s="20">
+        <f>IF(H3&gt;=1,"Completed",IF(...))</f>
+        <v/>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Multi-branch conditional logic</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>IFERROR</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>All formula columns</t>
+        </is>
+      </c>
+      <c r="C26" s="15">
+        <f>IFERROR(formula,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Return fallback if formula errors</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>2007+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>TODAY()</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Action Log — Days Overdue</t>
+        </is>
+      </c>
+      <c r="C27" s="20">
+        <f>IF(AND(I3&lt;&gt;"Closed",TODAY()&gt;G3),TODAY()-G3,"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Current date; updates on open</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>COLOR &amp; BADGE LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="61" t="n"/>
+      <c r="B31" s="62" t="inlineStr">
+        <is>
+          <t>Green badge</t>
+        </is>
+      </c>
+      <c r="C31" s="54" t="inlineStr">
+        <is>
+          <t>Completed · Closed · Resolved · Ahead · Low risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="63" t="n"/>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>Blue badge</t>
+        </is>
+      </c>
+      <c r="C32" s="54" t="inlineStr">
+        <is>
+          <t>Open · On Track · Mitigated · Material</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="65" t="n"/>
+      <c r="B33" s="66" t="inlineStr">
+        <is>
+          <t>Amber badge</t>
+        </is>
+      </c>
+      <c r="C33" s="54" t="inlineStr">
+        <is>
+          <t>In Progress · Medium · Workmanship · Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="67" t="n"/>
+      <c r="B34" s="68" t="inlineStr">
+        <is>
+          <t>Red badge</t>
+        </is>
+      </c>
+      <c r="C34" s="54" t="inlineStr">
+        <is>
+          <t>Overdue · High · Behind · Critical · Escalated</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="69" t="n"/>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>Gray badge</t>
+        </is>
+      </c>
+      <c r="C35" s="54" t="inlineStr">
+        <is>
+          <t>Not Started · On Hold · Neutral / N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="71" t="n"/>
+      <c r="B36" s="72" t="inlineStr">
+        <is>
+          <t>Teal badge</t>
+        </is>
+      </c>
+      <c r="C36" s="54" t="inlineStr">
+        <is>
+          <t>Installation type NCRs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="73" t="n"/>
+      <c r="B37" s="74" t="inlineStr">
+        <is>
+          <t>Surface row</t>
+        </is>
+      </c>
+      <c r="C37" s="54" t="inlineStr">
+        <is>
+          <t>Alternating data row background (barely visible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="75" t="n"/>
+      <c r="B38" s="76" t="inlineStr">
+        <is>
+          <t>Dark header</t>
+        </is>
+      </c>
+      <c r="C38" s="54" t="inlineStr">
+        <is>
+          <t>Column headers and section headers — uniform charcoal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="77" t="n"/>
+      <c r="B39" s="76" t="inlineStr">
+        <is>
+          <t>Ink title</t>
+        </is>
+      </c>
+      <c r="C39" s="54" t="inlineStr">
+        <is>
+          <t>Sheet titles — near-black</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A16:J16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9206,1585 +14195,1115 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00334155"/>
+    <tabColor rgb="001E293B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LOOKUP TABLES — Reference Data for Formula Calculations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Powers VLOOKUP · XLOOKUP · INDEX/MATCH across all sheets. Do not rename or delete this sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TABLE 1 · Discipline → Lead Person  (VLOOKUP / XLOOKUP / INDEX-MATCH reference)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>TABLE 2 · Risk Score Reference  (IFS formula band reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+          <t>WEEKLY SUBMISSION TRACKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Track which disciplines have submitted their weekly progress data  —  update each Monday by 09:00.  Amber = Pending.  Red = Overdue (not submitted by deadline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Lead Person</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Dept. Code</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Min Score</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Max Score</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>SLA Response</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 15
+14-Apr</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 16
+21-Apr</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 17
+28-Apr</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 18
+05-May</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 19
+12-May</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 20
+19-May</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 21
+26-May</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 22
+02-Jun</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 23
+09-Jun</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>Wk 24
+16-Jun</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>Submissions
+Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Civil</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>J. Hansen</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>j.hansen@project.com</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>Immediate action</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F4" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G4" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H4" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I4" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J4" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K4" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L4" s="48">
+        <f>COUNTIF(B4:K4,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>K. Lindqvist</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>k.lindqvist@project.com</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>Action within 14 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F5" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G5" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I5" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J5" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K5" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L5" s="50">
+        <f>COUNTIF(B5:K5,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>M. Berg</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>ELE</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>m.berg@project.com</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="25" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Monitor monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K6" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L6" s="48">
+        <f>COUNTIF(B6:K6,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A. Nilsen</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>MEC</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>a.nilsen@project.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F7" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G7" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I7" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J7" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K7" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L7" s="50">
+        <f>COUNTIF(B7:K7,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K8" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L8" s="48">
+        <f>COUNTIF(B8:K8,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Instrumentation</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>T. Eriksson</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>INS</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>t.eriksson@project.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Piping</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>S. Patel</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>PIP</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>s.patel@project.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K9" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L9" s="50">
+        <f>COUNTIF(B9:K9,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>HVAC</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>L. Andersen</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>HVA</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>l.andersen@project.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G10" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I10" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J10" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L10" s="48">
+        <f>COUNTIF(B10:K10,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>Scaffolding</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>R. Kowalski</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>r.kowalski@project.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>J. Hansen</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>j.hansen@project.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>TABLE 3 · Status Definitions &amp; Dropdown Values</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>TABLE 4 · Formula Index — Where Each Advanced Function Is Used</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Applies To</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Final?</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Actions / Risks / NCRs</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Raised, no action started</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>Weekly Progress</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="H18" s="15">
-        <f>H-G</f>
-        <v/>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Auto variance</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>Actions / NCRs</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>Work underway</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>Weekly Progress</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>IF nested</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>Auto status logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Fully resolved and verified</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>Weekly Progress</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>Responsible</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>XLOOKUP</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>From Lookup Tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Actions</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>Past due date — escalate</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Risk Register</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>Risk Score</t>
-        </is>
-      </c>
-      <c r="H21" s="20">
-        <f>E×F</f>
-        <v/>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>Auto P×I</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Risks</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Elevated to senior management</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>Risk Register</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>Risk Level</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="inlineStr">
-        <is>
-          <t>IF nested</t>
-        </is>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>From score</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Mitigated</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Risks</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>Mitigation complete; monitoring</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>Action Item Log</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>Responsible</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>VLOOKUP</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>From Lookup Tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Actions</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Blocked — awaiting input</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>Action Item Log</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>Days Overdue</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>IF/TODAY()</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Live days past due</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>NCR Tracker</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>Days Open</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>IF/TODAY()</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>Live days since raised</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>NCR Tracker</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>Discipline Lead</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>INDEX/MATCH</t>
-        </is>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>From Lookup Tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>Monthly Report</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>Schedule Var %</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>IFERROR/()</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>Auto SV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>Monthly Report</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>Cost Var %</t>
-        </is>
-      </c>
-      <c r="H28" s="15" t="inlineStr">
-        <is>
-          <t>IFERROR/()</t>
-        </is>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Auto CV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>Monthly Report</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>Discipline Lead</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>INDEX/MATCH</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>From Lookup Tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>DASHBOARD</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>All KPIs</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>COUNTIF</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Live from data sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>DASHBOARD</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>Discipline table</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>AVERAGEIF</t>
-        </is>
-      </c>
-      <c r="I31" s="20" t="inlineStr">
-        <is>
-          <t>Live pull per discipline</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>DASHBOARD</t>
-        </is>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>Monthly summary</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>SUMIFS</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Multi-criteria totals</t>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L11" s="50">
+        <f>COUNTIF(B11:K11,"Submitted")&amp;"/10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>Deadline: Every Monday 09:00 local time  |  Contact discipline lead directly if not submitted by 10:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="A16:D16"/>
+  <mergeCells count="3">
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B4:K11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Status" error="Choose: Submitted | Pending | Not Required | Overdue" promptTitle="Submission Status" prompt="Submitted = data received&#10;Pending = not yet received&#10;Not Required = discipline not active this week&#10;Overdue = deadline passed" type="list">
+      <formula1>"Submitted,Pending,Not Required,Overdue"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00334155"/>
+    <tabColor rgb="001E293B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="2" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
-    <col width="2" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>WORKBOOK GUIDE — Construction Project Data Management System</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Sheet directory, formula reference, color legend, ID conventions, and usage workflow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SHEET DIRECTORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Entry Columns</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Key Formulas</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Update Frequency</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Lookup Tables</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Reference tables — powers all lookup formulas</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Update when personnel changes</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>When team changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>DASHBOARD</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Live project health — KPIs, progress, risk, actions, EV</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>Read-only (formula-driven)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>COUNTIF/S, AVERAGEIF, SUMIFS</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Auto on file open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Weekly Progress</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Planned vs. actual % per activity per week</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>G (Planned%) and H (Actual%)</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>IF, XLOOKUP</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Weekly — by Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Risk Register</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Risk log with P×I matrix and auto level</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>All except G, H</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>E×F, nested IF</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Weekly minimum</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Action Item Log</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>All meeting action items with status tracking</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>All except F, N</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>VLOOKUP, IF/TODAY()</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>After each meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NCR Quality Tracker</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Non-conformance full lifecycle</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>All except M, N</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>TODAY()−date, INDEX/MATCH</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>As NCRs arise</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Monthly Report</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Budget vs. actual + Earned Value analysis</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>A–H, K–M</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>SV/CV formulas, INDEX/MATCH, SUMIFS</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>2nd working day</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Data Validation Log</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Data quality issues audit trail</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>All columns</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>Manual log</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>During validation sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>FORMULA REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Sheet — Column</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>COUNTIF</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Dashboard — KPI tiles</t>
-        </is>
-      </c>
-      <c r="C18" s="15">
-        <f>COUNTIF($I:$I,"Open")</f>
-        <v/>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Count matching single criterion</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>COUNTIFS</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>Dashboard — discipline table</t>
-        </is>
-      </c>
-      <c r="C19" s="20">
-        <f>COUNTIFS($E:$E,"Civil",$I:$I,"Open")</f>
-        <v/>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>Count matching multiple criteria</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>2007+</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>AVERAGEIF</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Dashboard — discipline %</t>
-        </is>
-      </c>
-      <c r="C20" s="15">
-        <f>AVERAGEIF($B:$B,"Civil",$H:$H)</f>
-        <v/>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Average matching one criterion</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>2007+</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>SUMIFS</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Dashboard — monthly summary</t>
-        </is>
-      </c>
-      <c r="C21" s="20">
-        <f>SUMIFS($C:$C,$A:$A,"Apr-26")</f>
-        <v/>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>Sum matching multiple criteria</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>2007+</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>VLOOKUP</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Action Log — Responsible col</t>
-        </is>
-      </c>
-      <c r="C22" s="15">
-        <f>IFERROR(VLOOKUP(E3,$A$6:$B$14,2,0),"-")</f>
-        <v/>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Lookup value in first column of table</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>XLOOKUP</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Weekly Progress — Responsible</t>
-        </is>
-      </c>
-      <c r="C23" s="20">
-        <f>IFERROR(XLOOKUP(B3,$A$6:$A$14,$B$6:$B$14),"?")</f>
-        <v/>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>Flexible; searches any direction</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>Excel 365</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>INDEX/MATCH</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>NCR &amp; Monthly — Disc. Lead</t>
-        </is>
-      </c>
-      <c r="C24" s="15">
-        <f>INDEX($B$6:$B$14,MATCH(B3,$A$6:$A$14,0))</f>
-        <v/>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Flexible alternative to VLOOKUP</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>IF nested</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>Weekly Progress — Status col</t>
-        </is>
-      </c>
-      <c r="C25" s="20">
-        <f>IF(H3&gt;=1,"Completed",IF(...))</f>
-        <v/>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>Multi-branch conditional logic</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>IFERROR</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>All formula columns</t>
-        </is>
-      </c>
-      <c r="C26" s="15">
-        <f>IFERROR(formula,0)</f>
-        <v/>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>Return fallback if formula errors</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>2007+</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>TODAY()</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Action Log — Days Overdue</t>
-        </is>
-      </c>
-      <c r="C27" s="20">
-        <f>IF(AND(I3&lt;&gt;"Closed",TODAY()&gt;G3),TODAY()-G3,"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>Current date; updates on open</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>COLOR &amp; BADGE LEGEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="45" t="n"/>
-      <c r="B31" s="46" t="inlineStr">
-        <is>
-          <t>Green badge</t>
-        </is>
-      </c>
-      <c r="C31" s="47" t="inlineStr">
-        <is>
-          <t>Completed · Closed · Resolved · Ahead · Low risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="48" t="n"/>
-      <c r="B32" s="49" t="inlineStr">
-        <is>
-          <t>Blue badge</t>
-        </is>
-      </c>
-      <c r="C32" s="47" t="inlineStr">
-        <is>
-          <t>Open · On Track · Mitigated · Material</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="50" t="n"/>
-      <c r="B33" s="51" t="inlineStr">
-        <is>
-          <t>Amber badge</t>
-        </is>
-      </c>
-      <c r="C33" s="47" t="inlineStr">
-        <is>
-          <t>In Progress · Medium · Workmanship · Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="52" t="n"/>
-      <c r="B34" s="53" t="inlineStr">
-        <is>
-          <t>Red badge</t>
-        </is>
-      </c>
-      <c r="C34" s="47" t="inlineStr">
-        <is>
-          <t>Overdue · High · Behind · Critical · Escalated</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="54" t="n"/>
-      <c r="B35" s="55" t="inlineStr">
-        <is>
-          <t>Gray badge</t>
-        </is>
-      </c>
-      <c r="C35" s="47" t="inlineStr">
-        <is>
-          <t>Not Started · On Hold · Neutral / N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="56" t="n"/>
-      <c r="B36" s="57" t="inlineStr">
-        <is>
-          <t>Teal badge</t>
-        </is>
-      </c>
-      <c r="C36" s="47" t="inlineStr">
-        <is>
-          <t>Installation type NCRs</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="58" t="n"/>
-      <c r="B37" s="59" t="inlineStr">
-        <is>
-          <t>Surface row</t>
-        </is>
-      </c>
-      <c r="C37" s="47" t="inlineStr">
-        <is>
-          <t>Alternating data row background (barely visible)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="60" t="n"/>
-      <c r="B38" s="61" t="inlineStr">
-        <is>
-          <t>Dark header</t>
-        </is>
-      </c>
-      <c r="C38" s="47" t="inlineStr">
-        <is>
-          <t>Column headers and section headers — uniform charcoal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="62" t="n"/>
-      <c r="B39" s="61" t="inlineStr">
-        <is>
-          <t>Ink title</t>
-        </is>
-      </c>
-      <c r="C39" s="47" t="inlineStr">
-        <is>
-          <t>Sheet titles — near-black</t>
-        </is>
+          <t>COORDINATION MEETING LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Record every coordination meeting  —  date, attendees, agenda items, decisions made, and action items raised.  Link action IDs to the Action Item Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Mtg #</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Meeting Type</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Chairperson</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Attendees (Disciplines)</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Agenda Item</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Discussion Summary</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Decision / Resolution</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Action IDs Raised</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Next Meeting Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Site Coordination</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>Civil, Structural, Electrical, Mechanical</t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="inlineStr">
+        <is>
+          <t>Progress review Wk 02</t>
+        </is>
+      </c>
+      <c r="G4" s="52" t="inlineStr">
+        <is>
+          <t>Civil 85% complete on earthworks. Structural material delivery confirmed for 20-Jan.</t>
+        </is>
+      </c>
+      <c r="H4" s="52" t="inlineStr">
+        <is>
+          <t>Proceed with foundation pour on 15-Jan pending QA sign-off.</t>
+        </is>
+      </c>
+      <c r="I4" s="52" t="inlineStr">
+        <is>
+          <t>AI-01, AI-02</t>
+        </is>
+      </c>
+      <c r="J4" s="53" t="n">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="n">
+        <v>46041</v>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Site Coordination</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>All disciplines</t>
+        </is>
+      </c>
+      <c r="F5" s="54" t="inlineStr">
+        <is>
+          <t>Progress review Wk 03 + NCR-001 close-out</t>
+        </is>
+      </c>
+      <c r="G5" s="54" t="inlineStr">
+        <is>
+          <t>NCR-001 closed. Electrical HV cabling 70% complete. Risk RR-05 escalated.</t>
+        </is>
+      </c>
+      <c r="H5" s="54" t="inlineStr">
+        <is>
+          <t>Electrical to submit HV route revision by 01-Feb. Safety walk scheduled 22-Jan.</t>
+        </is>
+      </c>
+      <c r="I5" s="54" t="inlineStr">
+        <is>
+          <t>AI-05</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="n">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="n">
+        <v>46055</v>
+      </c>
+      <c r="C6" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Site Coordination</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>Civil, Structural, Piping, Instrumentation</t>
+        </is>
+      </c>
+      <c r="F6" s="52" t="inlineStr">
+        <is>
+          <t>Progress review Wk 05 + schedule recovery</t>
+        </is>
+      </c>
+      <c r="G6" s="52" t="inlineStr">
+        <is>
+          <t>Piping behind by 5% due to spool delivery delay. Revised schedule presented.</t>
+        </is>
+      </c>
+      <c r="H6" s="52" t="inlineStr">
+        <is>
+          <t>Piping to recover 5% by Wk 08 through weekend work. Updated programme submitted.</t>
+        </is>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>AI-09, AI-10</t>
+        </is>
+      </c>
+      <c r="J6" s="53" t="n">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>Monthly Project Review</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>All disciplines + Client Representative</t>
+        </is>
+      </c>
+      <c r="F7" s="54" t="inlineStr">
+        <is>
+          <t>Feb progress vs baseline + EV summary</t>
+        </is>
+      </c>
+      <c r="G7" s="54" t="inlineStr">
+        <is>
+          <t>Overall SPI = 0.97. CPI = 1.02. Client satisfied with quality but flagged documentation gaps.</t>
+        </is>
+      </c>
+      <c r="H7" s="54" t="inlineStr">
+        <is>
+          <t>All disciplines to submit up-to-date as-builts by 28-Feb. Commissioning plan requested.</t>
+        </is>
+      </c>
+      <c r="I7" s="54" t="inlineStr">
+        <is>
+          <t>AI-04, AI-12</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="n">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Site Coordination</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>All disciplines</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>Progress review Wk 10 + risk review</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="inlineStr">
+        <is>
+          <t>High risk RR-01 (ground settlement) mitigated with ground improvement works. RR-14 new.</t>
+        </is>
+      </c>
+      <c r="H8" s="52" t="inlineStr">
+        <is>
+          <t>RR-14 (electrical isolation breach) added to register. Safety stand-down 04-Mar.</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="J8" s="53" t="n">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>M-06</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="n">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>Weekly Site Coordination</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>Structural, HVAC, Scaffolding</t>
+        </is>
+      </c>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>Scaffold inspection + HVAC commissioning prep</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>Scaffold passed inspection. HVAC ductwork leak test scheduled for 20-Mar.</t>
+        </is>
+      </c>
+      <c r="H9" s="54" t="inlineStr">
+        <is>
+          <t>HVAC to complete leak test and submit result by 25-Mar.</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="inlineStr">
+        <is>
+          <t>AI-13, AI-14</t>
+        </is>
+      </c>
+      <c r="J9" s="55" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
+        <is>
+          <t>M-07</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t>Weekly Site Coordination</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>All disciplines</t>
+        </is>
+      </c>
+      <c r="F10" s="52" t="inlineStr">
+        <is>
+          <t>Progress review Wk 15 + punch list kick-off</t>
+        </is>
+      </c>
+      <c r="G10" s="52" t="inlineStr">
+        <is>
+          <t>Punch list for Zone B steel started. 42 items raised across 3 disciplines.</t>
+        </is>
+      </c>
+      <c r="H10" s="52" t="inlineStr">
+        <is>
+          <t>Target: punch list clear by 30-Apr. Daily close-out meetings to start 08-Apr.</t>
+        </is>
+      </c>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>AI-17</t>
+        </is>
+      </c>
+      <c r="J10" s="53" t="n">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>M-08</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>Monthly Project Review</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>All disciplines + Client Representative</t>
+        </is>
+      </c>
+      <c r="F11" s="54" t="inlineStr">
+        <is>
+          <t>Apr progress + commissioning readiness</t>
+        </is>
+      </c>
+      <c r="G11" s="54" t="inlineStr">
+        <is>
+          <t>Overall project 78% complete against 80% planned. CPI remains above 1.0.</t>
+        </is>
+      </c>
+      <c r="H11" s="54" t="inlineStr">
+        <is>
+          <t>Commissioning plan approved. Mechanical completion target confirmed: 15-May.</t>
+        </is>
+      </c>
+      <c r="I11" s="54" t="inlineStr">
+        <is>
+          <t>AI-08, AI-11</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="n">
+        <v>46154</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A16:J16"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C4:C21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Meeting Type" prompt="Select the type of coordination meeting" type="list">
+      <formula1>"Weekly Site Coordination,Monthly Project Review,Safety Meeting,Client Meeting,Commissioning Meeting"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4:B21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Meeting Date" prompt="Enter date: DD-MMM-YY" type="date" operator="greaterThan">
+      <formula1>DATE(2020,1,1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>